--- a/src/utils/sxsyzlzq/friends/hezhongshan/zz_jiaozhu_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/hezhongshan/zz_jiaozhu_level.xlsx
@@ -7,13 +7,14 @@
     <workbookView windowWidth="27945" windowHeight="13395" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="萨维丽娅" sheetId="1" r:id="rId1"/>
-    <sheet name="亚芬戴克斯" sheetId="2" r:id="rId2"/>
-    <sheet name="伊萝莲" sheetId="3" r:id="rId3"/>
-    <sheet name="阿斯塔拉" sheetId="4" r:id="rId4"/>
+    <sheet name="伊萝莲" sheetId="3" r:id="rId1"/>
+    <sheet name="阿斯塔拉" sheetId="4" r:id="rId2"/>
+    <sheet name="丹巴瓦尔" sheetId="1" r:id="rId3"/>
+    <sheet name="尤瑞艾莉" sheetId="2" r:id="rId4"/>
     <sheet name="帝国" sheetId="5" r:id="rId5"/>
-    <sheet name="港口" sheetId="6" r:id="rId6"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId7"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId6"/>
+    <sheet name="蛮石" sheetId="8" r:id="rId7"/>
+    <sheet name="炼狱" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="87">
   <si>
     <t>名称</t>
   </si>
@@ -53,28 +54,25 @@
     <t>蓝色</t>
   </si>
   <si>
-    <t>心灵黑洞</t>
-  </si>
-  <si>
-    <t>圣殿卫士</t>
-  </si>
-  <si>
-    <t>狡诈学徒</t>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>方尖魔碑</t>
   </si>
   <si>
     <t>天使琼浆</t>
   </si>
   <si>
-    <t>黑夜突袭</t>
+    <t>沉重否定</t>
+  </si>
+  <si>
+    <t>增援战线</t>
   </si>
   <si>
     <t>圣殿弩手</t>
   </si>
   <si>
-    <t>热血矿工</t>
-  </si>
-  <si>
-    <t>增援战线</t>
+    <t>全数否定</t>
   </si>
   <si>
     <t>光明惩戒</t>
@@ -86,130 +84,175 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>四芒军旗</t>
+    <t>隐形术</t>
   </si>
   <si>
     <t>紫色</t>
   </si>
   <si>
-    <t>传记·钢铁守卫</t>
+    <t>破魔系教授</t>
   </si>
   <si>
     <t>圣殿御卫</t>
   </si>
   <si>
-    <t>海燕精卫</t>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型</t>
+  </si>
+  <si>
+    <t>边境高墙</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
+  </si>
+  <si>
+    <t>冲锋装备</t>
+  </si>
+  <si>
+    <t>夺取阵地</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>惩戒天使</t>
+  </si>
+  <si>
+    <t>禁卫指挥官</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>紫色卡等：</t>
+  </si>
+  <si>
+    <t>花光春影·安娜贝尔</t>
+  </si>
+  <si>
+    <t>橙色</t>
+  </si>
+  <si>
+    <t>百花长枪·卡罗琳</t>
+  </si>
+  <si>
+    <t>明日香·露娜</t>
+  </si>
+  <si>
+    <t>月之神·米拉</t>
+  </si>
+  <si>
+    <t>白袍·伊恩</t>
+  </si>
+  <si>
+    <t>橙色卡等：</t>
+  </si>
+  <si>
+    <t>总计：</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>幻域秘树</t>
+  </si>
+  <si>
+    <t>愚笨鲸头鹅</t>
+  </si>
+  <si>
+    <t>蓄力射手</t>
+  </si>
+  <si>
+    <t>旷野祭师</t>
+  </si>
+  <si>
+    <t>势如破竹</t>
+  </si>
+  <si>
+    <t>迅捷长矛手</t>
+  </si>
+  <si>
+    <t>天降碎石</t>
+  </si>
+  <si>
+    <t>强行捕猎</t>
+  </si>
+  <si>
+    <t>无畏猎户</t>
   </si>
   <si>
     <t>白袍主教</t>
   </si>
   <si>
-    <t>圣殿骑士</t>
-  </si>
-  <si>
-    <t>海盗船长</t>
-  </si>
-  <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>黑金诈术师</t>
-  </si>
-  <si>
-    <t>禁卫百夫长</t>
-  </si>
-  <si>
-    <t>禁卫指挥官</t>
-  </si>
-  <si>
-    <t>紫色卡等：</t>
-  </si>
-  <si>
-    <t>花光春影·安娜贝尔</t>
-  </si>
-  <si>
-    <t>橙色</t>
-  </si>
-  <si>
-    <t>百花长枪·卡罗琳</t>
-  </si>
-  <si>
-    <t>明日香·露娜</t>
+    <t>地洞巨獾</t>
+  </si>
+  <si>
+    <t>飞斧狂人</t>
+  </si>
+  <si>
+    <t>石斧头领</t>
+  </si>
+  <si>
+    <t>飞斧女豪</t>
+  </si>
+  <si>
+    <t>精灵王·大羽</t>
   </si>
   <si>
     <t>永恒之王·莱哈特</t>
   </si>
   <si>
-    <t>天雷降临·布瑞恩</t>
-  </si>
-  <si>
-    <t>白袍·伊恩</t>
-  </si>
-  <si>
-    <t>武圣·云长</t>
-  </si>
-  <si>
-    <t>橙色卡等：</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>魔力风暴</t>
-  </si>
-  <si>
-    <t>黑旗舰队水手</t>
-  </si>
-  <si>
-    <t>黑旗舰队飞斧手</t>
-  </si>
-  <si>
-    <t>烈日大祭师</t>
-  </si>
-  <si>
-    <t>蒙面侠客·翔</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>沉默否定</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>月之神·米拉</t>
-  </si>
-  <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>缄言法师</t>
-  </si>
-  <si>
-    <t>魔像-御咒铁卫</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>白首魔根</t>
+    <t>血饮烈斧·凯</t>
+  </si>
+  <si>
+    <t>白象战歌·鲁玛</t>
+  </si>
+  <si>
+    <t>落雷击</t>
+  </si>
+  <si>
+    <t>地狱刀吏</t>
+  </si>
+  <si>
+    <t>嗜血妖蛾</t>
+  </si>
+  <si>
+    <t>猩红勇士</t>
+  </si>
+  <si>
+    <t>地狱双头犬</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>绝望镰魔</t>
+  </si>
+  <si>
+    <t>岩浆球</t>
+  </si>
+  <si>
+    <t>雷光炼狱</t>
+  </si>
+  <si>
+    <t>地狱三头犬</t>
+  </si>
+  <si>
+    <t>恶灵魔焰</t>
+  </si>
+  <si>
+    <t>恶魔之心</t>
+  </si>
+  <si>
+    <t>岩魔</t>
+  </si>
+  <si>
+    <t>上古蛮王</t>
+  </si>
+  <si>
+    <t>怨魂饕餮兽</t>
   </si>
   <si>
     <t>曙光·安娜贝尔</t>
@@ -227,25 +270,31 @@
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>花剑绅士·翔</t>
-  </si>
-  <si>
-    <t>钢之咆哮·布瑞恩</t>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>旷野游侠·大羽</t>
+  </si>
+  <si>
+    <t>原野大祭师·鲁玛</t>
   </si>
   <si>
     <t>港口卡等：</t>
   </si>
   <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
+    <t>痛苦之心</t>
+  </si>
+  <si>
+    <t>血影</t>
+  </si>
+  <si>
+    <t>巴克&amp;巴罗</t>
   </si>
 </sst>
 </file>
@@ -1251,12 +1300,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1265,7 +1314,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1276,10 +1325,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1293,7 +1342,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1307,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1321,7 +1370,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1332,10 +1381,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1349,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1363,7 +1412,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1374,102 +1423,102 @@
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1">
-        <v>17</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>17</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="D14" s="1">
+        <f>AVERAGE(D2:D11)</f>
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
-        <f>AVERAGE(D2:D13)</f>
-        <v>17.6666666666667</v>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
         <v>20</v>
@@ -1480,66 +1529,66 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
         <v>18</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26" s="2">
         <v>15</v>
@@ -1547,110 +1596,109 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
         <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="2">
+        <v>5</v>
+      </c>
+      <c r="D28" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="2">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2">
-        <v>17</v>
-      </c>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="B29" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2">
         <v>6</v>
       </c>
       <c r="D29" s="2">
-        <v>17</v>
-      </c>
-      <c r="F29" s="5"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="A30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2">
+        <v>6</v>
+      </c>
+      <c r="D30" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="2">
+        <v>7</v>
+      </c>
+      <c r="D31" s="2">
+        <v>14</v>
+      </c>
+      <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D19:D29)</f>
-        <v>16.7272727272727</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="3">
-        <v>4</v>
-      </c>
-      <c r="D36" s="3">
-        <v>18</v>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2">
+        <f>AVERAGE(D17:D31)</f>
+        <v>15.2</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="3">
         <v>14</v>
@@ -1658,55 +1706,55 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C41" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" s="3">
         <v>16</v>
@@ -1726,26 +1774,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D35:D41)</f>
-        <v>15.8571428571429</v>
+        <f>AVERAGE(D37:D41)</f>
+        <v>14.4</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D13,D19:D29,D35:D41)</f>
-        <v>16.9</v>
+        <f>AVERAGE(D2:D11,D17:D31,D37:D41)</f>
+        <v>15.7666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1790,12 +1838,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1804,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1815,24 +1863,24 @@
         <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1846,12 +1894,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -1860,12 +1908,12 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -1879,7 +1927,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -1888,12 +1936,12 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
@@ -1902,113 +1950,113 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="1">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1">
-        <v>15</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="1">
-        <v>4</v>
-      </c>
-      <c r="D13" s="1">
-        <v>15</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1">
-        <v>5</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="1">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
+        <f>AVERAGE(D2:D11)</f>
+        <v>17.3</v>
+      </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
         <v>15</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
-        <f>AVERAGE(D2:D15)</f>
-        <v>16.4285714285714</v>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
         <v>20</v>
@@ -2019,91 +2067,91 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2">
         <v>18</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2">
-        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
         <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2">
         <v>5</v>
@@ -2111,84 +2159,86 @@
       <c r="D28" s="2">
         <v>13</v>
       </c>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4">
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2">
+        <v>6</v>
+      </c>
+      <c r="D29" s="2">
+        <v>14</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2">
+        <v>6</v>
+      </c>
+      <c r="D30" s="2">
+        <v>13</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C31" s="2">
+        <v>7</v>
+      </c>
       <c r="D31" s="2">
-        <f>AVERAGE(D21:D28)</f>
-        <v>16.75</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="3">
-        <v>2</v>
-      </c>
-      <c r="D34" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="3">
-        <v>4</v>
-      </c>
-      <c r="D36" s="3">
-        <v>18</v>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2">
+        <f>AVERAGE(D17:D31)</f>
+        <v>15.2</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" s="3">
         <v>14</v>
@@ -2196,55 +2246,55 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C41" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D41" s="3">
         <v>16</v>
@@ -2264,31 +2314,30 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D34:D41)</f>
-        <v>15.5</v>
+        <f>AVERAGE(D37:D41)</f>
+        <v>14.4</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D15,D21:D28,D34:D41)</f>
-        <v>16.2666666666667</v>
+        <f>AVERAGE(D2:D11,D17:D31,D37:D41)</f>
+        <v>15.7666666666667</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -2319,41 +2368,41 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>18</v>
@@ -2361,7 +2410,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2370,12 +2419,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2384,26 +2433,26 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
@@ -2417,7 +2466,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
@@ -2426,244 +2475,237 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <f>AVERAGE(D2:D11)</f>
-        <v>17.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="2">
-        <v>1</v>
-      </c>
-      <c r="D18" s="2">
-        <v>15</v>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <f>AVERAGE(D2:D13)</f>
+        <v>15.9166666666667</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
       </c>
       <c r="D27" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="2">
-        <v>7</v>
-      </c>
-      <c r="D29" s="2">
-        <v>14</v>
-      </c>
-      <c r="F29" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2"/>
@@ -2672,92 +2714,100 @@
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="A31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D17:D29)</f>
-        <v>15.6923076923077</v>
+      <c r="D31" s="2">
+        <f>AVERAGE(D19:D28)</f>
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3</v>
+      </c>
+      <c r="D34" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C35" s="3">
         <v>3</v>
       </c>
       <c r="D35" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C36" s="3">
         <v>4</v>
       </c>
       <c r="D36" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="3">
         <v>4</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" s="3">
         <v>5</v>
       </c>
       <c r="D38" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" s="3">
         <v>5</v>
       </c>
       <c r="D39" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2765,7 +2815,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" s="3">
         <v>6</v>
@@ -2776,16 +2826,16 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C41" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2802,26 +2852,26 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D35:D41)</f>
-        <v>15.5714285714286</v>
+        <f>AVERAGE(D34:D41)</f>
+        <v>13.375</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D11,D17:D29,D35:D41)</f>
-        <v>16.2</v>
+        <f>AVERAGE(D2:D13,D19:D28,D34:D41)</f>
+        <v>14.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2857,7 +2907,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -2866,12 +2916,12 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2885,7 +2935,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>5</v>
@@ -2894,12 +2944,12 @@
         <v>2</v>
       </c>
       <c r="D4" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
@@ -2908,12 +2958,12 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -2922,12 +2972,12 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>5</v>
@@ -2936,127 +2986,127 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
-        <f>AVERAGE(D2:D9)</f>
-        <v>16.375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="2">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2">
-        <v>13</v>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
+        <f>AVERAGE(D2:D11)</f>
+        <v>14.1</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="2">
         <v>14</v>
@@ -3064,108 +3114,111 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2">
         <v>18</v>
-      </c>
-      <c r="C22" s="2">
-        <v>4</v>
-      </c>
-      <c r="D22" s="2">
-        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2">
         <v>4</v>
       </c>
       <c r="D25" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>15</v>
+      </c>
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="2">
         <v>5</v>
@@ -3173,158 +3226,161 @@
       <c r="D27" s="2">
         <v>13</v>
       </c>
+      <c r="F27" s="5"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F28" s="5"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="2">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2">
+        <v>10</v>
+      </c>
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2">
+        <v>6</v>
+      </c>
+      <c r="D30" s="2">
+        <v>11</v>
+      </c>
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="2">
         <v>7</v>
       </c>
-      <c r="D29" s="2">
-        <v>14</v>
-      </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="D31" s="2">
+        <v>14</v>
+      </c>
+      <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <f>AVERAGE(D15:D29)</f>
-        <v>14.3333333333333</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C35" s="3">
-        <v>3</v>
-      </c>
-      <c r="D35" s="3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="3">
-        <v>4</v>
-      </c>
-      <c r="D36" s="3">
-        <v>18</v>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2">
+        <f>AVERAGE(D17:D31)</f>
+        <v>14.0666666666667</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="3" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C38" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D38" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C39" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C41" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D41" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3341,30 +3397,31 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3">
-        <f>AVERAGE(D35:D41)</f>
-        <v>15.5714285714286</v>
+        <f>AVERAGE(D37:D41)</f>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4">
-        <f>AVERAGE(D2:D9,D15:D29,D35:D41)</f>
-        <v>15.1666666666667</v>
+        <f>AVERAGE(D2:D11,D17:D31,D37:D41)</f>
+        <v>13.5666666666667</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3372,7 +3429,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -3399,34 +3456,34 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -3437,66 +3494,66 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>17</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1">
-        <f>AVERAGE(C2:C8)</f>
-        <v>18.7142857142857</v>
-      </c>
-      <c r="D11" s="2"/>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>17.5</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
         <v>16</v>
@@ -3504,10 +3561,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B15" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
         <v>15</v>
@@ -3515,46 +3572,46 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -3562,22 +3619,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="2">
-        <v>6</v>
-      </c>
-      <c r="C21" s="2">
-        <v>17</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2"/>
@@ -3585,120 +3636,104 @@
       <c r="C22" s="2"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="2">
-        <f>AVERAGE(C14:C21)</f>
-        <v>17</v>
+      <c r="A23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C13:C20)</f>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B27" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B28" s="3">
         <v>4</v>
       </c>
       <c r="C28" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B29" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C30" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="3">
-        <v>6</v>
-      </c>
-      <c r="C31" s="3">
-        <v>16</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B32" s="3">
-        <v>8</v>
-      </c>
-      <c r="C32" s="3">
-        <v>16</v>
-      </c>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="3" t="s">
+      <c r="A33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="3">
+        <f>AVERAGE(C26:C30)</f>
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="3">
-        <f>AVERAGE(C27:C32)</f>
-        <v>16.1666666666667</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" s="4">
-        <f>AVERAGE(C2:C8,C14:C21,C27:C32)</f>
-        <v>17.3333333333333</v>
+      <c r="B36" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C36" s="4">
+        <f>AVERAGE(C2:C7,C13:C20,C26:C30)</f>
+        <v>15.4736842105263</v>
       </c>
     </row>
   </sheetData>
@@ -3734,129 +3769,129 @@
         <v>6</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>17</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="1">
-        <v>5</v>
-      </c>
-      <c r="C10" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>15.2222222222222</v>
-      </c>
-      <c r="D13" s="2"/>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>18</v>
@@ -3864,29 +3899,29 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
       </c>
       <c r="C17" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
       </c>
       <c r="C18" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2">
         <v>5</v>
@@ -3896,9 +3931,15 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="2">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2"/>
@@ -3906,31 +3947,25 @@
       <c r="C21" s="2"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C16:C19)</f>
-        <v>15.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="3">
-        <v>2</v>
-      </c>
-      <c r="C25" s="3">
-        <v>13</v>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C11:C20)</f>
+        <v>15.7</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
@@ -3951,26 +3986,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>13.5</v>
+        <f>AVERAGE(C26:C26)</f>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
-        <v>15</v>
+        <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
+        <v>15.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4003,118 +4038,118 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="1">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>14.25</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
-        <v>14</v>
-      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>14.5714285714286</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -4125,87 +4160,87 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
-        <v>13</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="2">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2">
-        <v>14</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="2">
-        <f>AVERAGE(C11:C20)</f>
-        <v>12.9</v>
+      <c r="A21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C14:C18)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25" s="3">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3">
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
         <v>13</v>
@@ -4223,26 +4258,298 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C26:C26)</f>
-        <v>13</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>11.3333333333333</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C20,C26:C26)</f>
-        <v>13.2666666666667</v>
+        <f>AVERAGE(C2:C8,C14:C18,C24:C26)</f>
+        <v>13.7333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1">
+        <f>AVERAGE(C2:C7)</f>
+        <v>13.5</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
+      <c r="C15" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C13:C17)</f>
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="3">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C23:C26)</f>
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C7,C13:C17,C23:C26)</f>
+        <v>11.7333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/src/utils/sxsyzlzq/friends/hezhongshan/zz_jiaozhu_level.xlsx
+++ b/src/utils/sxsyzlzq/friends/hezhongshan/zz_jiaozhu_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="13395" activeTab="6"/>
+    <workbookView windowWidth="27945" windowHeight="13395" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="伊萝莲" sheetId="3" r:id="rId1"/>
@@ -3696,7 +3696,7 @@
         <v>77</v>
       </c>
       <c r="B30" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="3">
         <v>16</v>
